--- a/Expenses2023.xlsx
+++ b/Expenses2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E334111-FDA9-4E06-9DB7-BA532CC6C3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D75D17-7798-419C-BCBF-B9D2D9584E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="11" r:id="rId1"/>
@@ -48003,9 +48003,12 @@
       <c r="Z118" s="13">
         <v>15</v>
       </c>
+      <c r="AA118" s="13">
+        <v>181</v>
+      </c>
       <c r="AH118">
         <f t="shared" si="4"/>
-        <v>8141.29</v>
+        <v>8322.2900000000009</v>
       </c>
       <c r="AI118" s="2" t="s">
         <v>89</v>

--- a/Expenses2023.xlsx
+++ b/Expenses2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D75D17-7798-419C-BCBF-B9D2D9584E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814B12CF-9146-4759-9F2A-BBB8F88B2064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="11" r:id="rId1"/>
@@ -451,7 +451,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="102">
   <si>
     <t>Petrol</t>
   </si>
@@ -754,6 +754,9 @@
   </si>
   <si>
     <t>Toll</t>
+  </si>
+  <si>
+    <t>Internet</t>
   </si>
 </sst>
 </file>
@@ -44354,7 +44357,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA1C94F-A213-4720-95FA-D2049096F275}">
-  <dimension ref="A1:AK119"/>
+  <dimension ref="A1:AK141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -47509,9 +47512,18 @@
       <c r="Z96">
         <v>27</v>
       </c>
+      <c r="AA96">
+        <v>28</v>
+      </c>
+      <c r="AC96">
+        <v>55</v>
+      </c>
+      <c r="AE96">
+        <v>28</v>
+      </c>
       <c r="AH96">
         <f>SUM(B96:AF96)</f>
-        <v>721</v>
+        <v>832</v>
       </c>
       <c r="AI96" s="2" t="s">
         <v>5</v>
@@ -47545,9 +47557,15 @@
       <c r="Y98">
         <v>200</v>
       </c>
+      <c r="AE98">
+        <v>1250</v>
+      </c>
+      <c r="AF98">
+        <v>1250</v>
+      </c>
       <c r="AH98">
-        <f t="shared" ref="AH98:AH118" si="4">SUM(B98:AF98)</f>
-        <v>800</v>
+        <f t="shared" ref="AH98:AH117" si="4">SUM(B98:AF98)</f>
+        <v>3300</v>
       </c>
       <c r="AI98" s="2" t="s">
         <v>0</v>
@@ -47587,9 +47605,12 @@
       <c r="Y99">
         <v>500</v>
       </c>
+      <c r="AF99">
+        <v>50</v>
+      </c>
       <c r="AH99">
         <f t="shared" si="4"/>
-        <v>1646</v>
+        <v>1696</v>
       </c>
       <c r="AI99" s="2" t="s">
         <v>16</v>
@@ -47632,9 +47653,15 @@
       <c r="X101">
         <v>856.1</v>
       </c>
+      <c r="AE101">
+        <v>109</v>
+      </c>
+      <c r="AF101">
+        <v>50</v>
+      </c>
       <c r="AH101">
         <f t="shared" si="4"/>
-        <v>2759.34</v>
+        <v>2918.34</v>
       </c>
       <c r="AI101" s="2" t="s">
         <v>18</v>
@@ -47677,9 +47704,18 @@
       <c r="Y102">
         <v>420</v>
       </c>
+      <c r="AC102">
+        <v>150</v>
+      </c>
+      <c r="AD102">
+        <v>38</v>
+      </c>
+      <c r="AF102">
+        <v>180</v>
+      </c>
       <c r="AH102">
         <f t="shared" si="4"/>
-        <v>1296</v>
+        <v>1664</v>
       </c>
       <c r="AI102" s="2" t="s">
         <v>2</v>
@@ -47704,9 +47740,15 @@
       <c r="X103">
         <v>71.75</v>
       </c>
+      <c r="AD103">
+        <v>20</v>
+      </c>
+      <c r="AF103">
+        <v>180</v>
+      </c>
       <c r="AH103">
         <f t="shared" si="4"/>
-        <v>425.75</v>
+        <v>625.75</v>
       </c>
       <c r="AI103" s="2" t="s">
         <v>19</v>
@@ -47780,251 +47822,719 @@
     </row>
     <row r="107" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>99</v>
+        <v>11</v>
+      </c>
+      <c r="O107">
+        <v>925</v>
       </c>
       <c r="AH107">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="AI107" s="2" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O108">
-        <v>925</v>
+        <v>31</v>
+      </c>
+      <c r="V108">
+        <v>20</v>
       </c>
       <c r="AH108">
         <f t="shared" si="4"/>
-        <v>925</v>
+        <v>20</v>
       </c>
       <c r="AI108" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V109">
-        <v>20</v>
+        <v>99</v>
+      </c>
+      <c r="C109">
+        <v>200</v>
+      </c>
+      <c r="Y109">
+        <v>80</v>
       </c>
       <c r="AH109">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="AI109" s="2" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="C110">
-        <v>200</v>
-      </c>
-      <c r="Y110">
-        <v>80</v>
+        <v>499</v>
       </c>
       <c r="AH110">
         <f t="shared" si="4"/>
-        <v>280</v>
+        <v>499</v>
       </c>
       <c r="AI110" s="2" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C111">
-        <v>499</v>
+        <v>92</v>
       </c>
       <c r="AH111">
         <f t="shared" si="4"/>
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="AI111" s="2" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="AF112">
+        <v>250</v>
       </c>
       <c r="AH112">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AI112" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>100</v>
+        <v>12</v>
+      </c>
+      <c r="C113">
+        <v>300</v>
+      </c>
+      <c r="E113">
+        <v>1499</v>
+      </c>
+      <c r="F113">
+        <v>30</v>
+      </c>
+      <c r="G113">
+        <v>15</v>
+      </c>
+      <c r="I113">
+        <v>320</v>
+      </c>
+      <c r="V113">
+        <v>50</v>
+      </c>
+      <c r="W113">
+        <v>656</v>
+      </c>
+      <c r="Y113">
+        <v>2060</v>
+      </c>
+      <c r="AC113">
+        <v>250</v>
       </c>
       <c r="AH113">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5180</v>
       </c>
       <c r="AI113" s="2" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C114">
-        <v>300</v>
-      </c>
-      <c r="E114">
-        <v>1499</v>
-      </c>
-      <c r="F114">
         <v>30</v>
       </c>
-      <c r="G114">
-        <v>15</v>
-      </c>
-      <c r="I114">
-        <v>320</v>
-      </c>
-      <c r="V114">
-        <v>50</v>
-      </c>
-      <c r="W114">
-        <v>656</v>
-      </c>
-      <c r="Y114">
-        <v>2060</v>
+      <c r="AF114">
+        <v>200</v>
       </c>
       <c r="AH114">
         <f t="shared" si="4"/>
-        <v>4930</v>
+        <v>200</v>
       </c>
       <c r="AI114" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="M115">
+        <v>49</v>
       </c>
       <c r="AH115">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AI115" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M116">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="C116">
+        <v>100</v>
+      </c>
+      <c r="K116">
+        <v>350</v>
+      </c>
+      <c r="L116">
+        <v>15</v>
+      </c>
+      <c r="N116">
+        <v>18285</v>
+      </c>
+      <c r="V116">
+        <v>50</v>
       </c>
       <c r="AH116">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>18800</v>
       </c>
       <c r="AI116" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C117">
-        <v>100</v>
-      </c>
-      <c r="K117">
-        <v>350</v>
-      </c>
-      <c r="L117">
+        <v>89</v>
+      </c>
+      <c r="G117" s="13">
+        <v>10</v>
+      </c>
+      <c r="H117" s="13">
+        <v>50</v>
+      </c>
+      <c r="I117" s="13">
+        <v>26</v>
+      </c>
+      <c r="J117" s="13"/>
+      <c r="K117" s="13"/>
+      <c r="L117" s="13">
+        <v>198</v>
+      </c>
+      <c r="N117" s="13">
+        <v>256</v>
+      </c>
+      <c r="U117" s="13">
+        <v>26</v>
+      </c>
+      <c r="V117" s="13">
+        <v>7271</v>
+      </c>
+      <c r="W117" s="13">
+        <v>269.29000000000002</v>
+      </c>
+      <c r="Y117" s="13">
+        <v>20</v>
+      </c>
+      <c r="Z117" s="13">
         <v>15</v>
       </c>
-      <c r="N117">
-        <v>18285</v>
-      </c>
-      <c r="V117">
-        <v>50</v>
+      <c r="AA117" s="13">
+        <v>181</v>
+      </c>
+      <c r="AB117" s="13">
+        <v>440</v>
+      </c>
+      <c r="AD117" s="13">
+        <v>88</v>
+      </c>
+      <c r="AE117" s="13">
+        <v>153</v>
       </c>
       <c r="AH117">
         <f t="shared" si="4"/>
-        <v>18800</v>
+        <v>9003.2900000000009</v>
       </c>
       <c r="AI117" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="Q118" s="6">
+        <f>SUM(B96:AF116)</f>
+        <v>40796.74</v>
+      </c>
+      <c r="R118">
+        <v>-18285</v>
+      </c>
+      <c r="AJ118">
+        <f>SUM(AJ94,Q118)</f>
+        <v>318326.56</v>
+      </c>
+    </row>
+    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B119" s="1">
+        <v>46174</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46175</v>
+      </c>
+      <c r="D119" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E119" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F119" s="1">
+        <v>46178</v>
+      </c>
+      <c r="G119" s="1">
+        <v>46179</v>
+      </c>
+      <c r="H119" s="1">
+        <v>46180</v>
+      </c>
+      <c r="I119" s="1">
+        <v>46181</v>
+      </c>
+      <c r="J119" s="1">
+        <v>46182</v>
+      </c>
+      <c r="K119" s="1">
+        <v>46183</v>
+      </c>
+      <c r="L119" s="1">
+        <v>46184</v>
+      </c>
+      <c r="M119" s="1">
+        <v>46185</v>
+      </c>
+      <c r="N119" s="1">
+        <v>46186</v>
+      </c>
+      <c r="O119" s="1">
+        <v>46187</v>
+      </c>
+      <c r="P119" s="1">
+        <v>46188</v>
+      </c>
+      <c r="Q119" s="1">
+        <v>46189</v>
+      </c>
+      <c r="R119" s="1">
+        <v>46190</v>
+      </c>
+      <c r="S119" s="1">
+        <v>46191</v>
+      </c>
+      <c r="T119" s="1">
+        <v>46192</v>
+      </c>
+      <c r="U119" s="1">
+        <v>46193</v>
+      </c>
+      <c r="V119" s="1">
+        <v>46194</v>
+      </c>
+      <c r="W119" s="1">
+        <v>46195</v>
+      </c>
+      <c r="X119" s="1">
+        <v>46196</v>
+      </c>
+      <c r="Y119" s="1">
+        <v>46197</v>
+      </c>
+      <c r="Z119" s="1">
+        <v>46198</v>
+      </c>
+      <c r="AA119" s="1">
+        <v>46199</v>
+      </c>
+      <c r="AB119" s="1">
+        <v>46200</v>
+      </c>
+      <c r="AC119" s="1">
+        <v>46201</v>
+      </c>
+      <c r="AD119" s="1">
+        <v>46202</v>
+      </c>
+      <c r="AE119" s="1">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="120" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120">
+        <v>55</v>
+      </c>
+      <c r="C120">
+        <v>28</v>
+      </c>
+      <c r="D120">
+        <v>27</v>
+      </c>
+      <c r="E120">
+        <v>28</v>
+      </c>
+      <c r="F120">
+        <v>55</v>
+      </c>
+      <c r="G120">
+        <v>28</v>
+      </c>
+      <c r="H120">
+        <v>54.5</v>
+      </c>
+      <c r="AH120">
+        <f>SUM(B120:AE120)</f>
+        <v>275.5</v>
+      </c>
+      <c r="AI120" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH121">
+        <f>SUM(B121:AE121)</f>
+        <v>0</v>
+      </c>
+      <c r="AI121" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" s="5">
+        <v>200</v>
+      </c>
+      <c r="H122">
+        <v>200</v>
+      </c>
+      <c r="AH122">
+        <f>SUM(B122:AE122)</f>
+        <v>400</v>
+      </c>
+      <c r="AI122" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B123">
+        <v>68</v>
+      </c>
+      <c r="E123">
+        <v>18</v>
+      </c>
+      <c r="H123">
+        <v>648</v>
+      </c>
+      <c r="AH123">
+        <f t="shared" ref="AH123:AH140" si="5">SUM(B123:AE123)</f>
+        <v>734</v>
+      </c>
+      <c r="AI123" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H124">
+        <v>69.05</v>
+      </c>
+      <c r="AH124">
+        <f t="shared" si="5"/>
+        <v>69.05</v>
+      </c>
+      <c r="AI124" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="125" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B125">
+        <v>40</v>
+      </c>
+      <c r="H125">
+        <v>1474.72</v>
+      </c>
+      <c r="J125">
+        <v>177</v>
+      </c>
+      <c r="AH125">
+        <f t="shared" si="5"/>
+        <v>1691.72</v>
+      </c>
+      <c r="AI125" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B126">
+        <v>27</v>
+      </c>
+      <c r="C126">
+        <v>34</v>
+      </c>
+      <c r="D126">
+        <v>30</v>
+      </c>
+      <c r="F126">
+        <v>34</v>
+      </c>
+      <c r="H126">
+        <v>250</v>
+      </c>
+      <c r="AH126">
+        <f t="shared" si="5"/>
+        <v>375</v>
+      </c>
+      <c r="AI126" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127">
+        <v>70</v>
+      </c>
+      <c r="G127">
+        <v>80</v>
+      </c>
+      <c r="AH127">
+        <f t="shared" si="5"/>
+        <v>150</v>
+      </c>
+      <c r="AI127" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B128">
+        <v>50</v>
+      </c>
+      <c r="C128">
+        <v>100</v>
+      </c>
+      <c r="H128">
+        <v>50</v>
+      </c>
+      <c r="AH128">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="AI128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH129">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI129" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH130">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI130" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131">
+        <v>556.82000000000005</v>
+      </c>
+      <c r="AH131">
+        <f t="shared" si="5"/>
+        <v>556.82000000000005</v>
+      </c>
+      <c r="AI131" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="132" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH132">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI132" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="133" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B133">
+        <v>150</v>
+      </c>
+      <c r="F133">
+        <v>647.82000000000005</v>
+      </c>
+      <c r="H133">
+        <v>40</v>
+      </c>
+      <c r="AH133">
+        <f t="shared" si="5"/>
+        <v>837.82</v>
+      </c>
+      <c r="AI133" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH134">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI134" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="135" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI135" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH136">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B137">
+        <v>10</v>
+      </c>
+      <c r="C137">
+        <v>40</v>
+      </c>
+      <c r="AH137">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="AI137" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH138">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI138" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+      <c r="AH139">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI139" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G118" s="13">
-        <v>10</v>
-      </c>
-      <c r="H118" s="13">
-        <v>50</v>
-      </c>
-      <c r="I118" s="13">
+      <c r="C140" s="13">
+        <v>30</v>
+      </c>
+      <c r="F140" s="13">
         <v>26</v>
       </c>
-      <c r="J118" s="13"/>
-      <c r="K118" s="13"/>
-      <c r="L118" s="13">
-        <v>198</v>
-      </c>
-      <c r="N118" s="13">
-        <v>256</v>
-      </c>
-      <c r="U118" s="13">
+      <c r="I140" s="13">
+        <v>60</v>
+      </c>
+      <c r="J140" s="13">
         <v>26</v>
       </c>
-      <c r="V118" s="13">
-        <v>7271</v>
-      </c>
-      <c r="W118" s="13">
-        <v>269.29000000000002</v>
-      </c>
-      <c r="Y118" s="13">
-        <v>20</v>
-      </c>
-      <c r="Z118" s="13">
-        <v>15</v>
-      </c>
-      <c r="AA118" s="13">
-        <v>181</v>
-      </c>
-      <c r="AH118">
-        <f t="shared" si="4"/>
-        <v>8322.2900000000009</v>
-      </c>
-      <c r="AI118" s="2" t="s">
+      <c r="AH140">
+        <f t="shared" si="5"/>
+        <v>142</v>
+      </c>
+      <c r="AI140" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="Q119" s="6">
-        <f>SUM(B96:AF117)</f>
-        <v>36708.740000000005</v>
-      </c>
-      <c r="R119">
-        <v>-18285</v>
-      </c>
-      <c r="AJ119">
-        <f>SUM(AJ94,Q119)</f>
-        <v>314238.56</v>
+    <row r="141" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="Q141" s="6">
+        <f>SUM(B120:AE139)</f>
+        <v>5339.91</v>
+      </c>
+      <c r="AJ141">
+        <f>SUM(AJ118,Q141)</f>
+        <v>323666.46999999997</v>
       </c>
     </row>
   </sheetData>

--- a/Expenses2023.xlsx
+++ b/Expenses2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814B12CF-9146-4759-9F2A-BBB8F88B2064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8FEEFD-3B1B-4960-836E-09625146DC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2023'!$A$1:$AF$244</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2024'!$A$1:$AF$243</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2025'!$A$1:$AF$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2026'!$A$1:$AF$164</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -451,7 +452,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2309" uniqueCount="104">
   <si>
     <t>Petrol</t>
   </si>
@@ -757,6 +758,12 @@
   </si>
   <si>
     <t>Internet</t>
+  </si>
+  <si>
+    <t>Tithi</t>
+  </si>
+  <si>
+    <t>DeepaOil</t>
   </si>
 </sst>
 </file>
@@ -35883,7 +35890,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D8B105-7B1D-4CC9-AC70-0A198640A3CC}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ264"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -35992,7 +35998,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="2" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -36088,7 +36094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -36100,7 +36106,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -36130,7 +36136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -36184,7 +36190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -36199,7 +36205,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -36238,7 +36244,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
@@ -36277,7 +36283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -36331,7 +36337,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -36364,7 +36370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -36388,7 +36394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -36403,7 +36409,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -36418,7 +36424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -36445,7 +36451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>31</v>
       </c>
@@ -36495,7 +36501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -36513,7 +36519,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -36528,7 +36534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
@@ -36549,7 +36555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
@@ -36579,13 +36585,13 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="Q21" s="6">
         <f>SUM(B2:AF19)</f>
         <v>20986.74</v>
       </c>
     </row>
-    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>45689</v>
       </c>
@@ -36671,7 +36677,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
@@ -36752,7 +36758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -36767,7 +36773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>0</v>
       </c>
@@ -36788,7 +36794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>16</v>
       </c>
@@ -36849,7 +36855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
@@ -36868,7 +36874,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>18</v>
       </c>
@@ -36901,7 +36907,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>2</v>
       </c>
@@ -36955,7 +36961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
@@ -36997,7 +37003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -37024,7 +37030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
@@ -37048,7 +37054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
@@ -37063,7 +37069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>17</v>
       </c>
@@ -37081,7 +37087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>20</v>
       </c>
@@ -37102,7 +37108,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -37117,7 +37123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
@@ -37132,7 +37138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>90</v>
       </c>
@@ -37174,7 +37180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -37189,7 +37195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
@@ -37207,7 +37213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>4</v>
       </c>
@@ -37225,7 +37231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>89</v>
       </c>
@@ -37246,7 +37252,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="44" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q44" s="6">
         <f>SUM(B23:AC42)</f>
         <v>22311.629999999997</v>
@@ -37256,7 +37262,7 @@
         <v>43298.369999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B45" s="1">
         <v>45717</v>
       </c>
@@ -37351,7 +37357,7 @@
         <v>45747</v>
       </c>
     </row>
-    <row r="46" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>5</v>
       </c>
@@ -37411,7 +37417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -37432,7 +37438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>16</v>
       </c>
@@ -37489,7 +37495,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>34</v>
       </c>
@@ -37508,7 +37514,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -37553,7 +37559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>2</v>
       </c>
@@ -37595,7 +37601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>19</v>
       </c>
@@ -37640,7 +37646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
@@ -37664,7 +37670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>15</v>
       </c>
@@ -37688,7 +37694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>13</v>
       </c>
@@ -37703,7 +37709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>17</v>
       </c>
@@ -37718,7 +37724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>20</v>
       </c>
@@ -37742,7 +37748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>8</v>
       </c>
@@ -37784,7 +37790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>4</v>
       </c>
@@ -37802,7 +37808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>89</v>
       </c>
@@ -37842,7 +37848,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q62" s="6">
         <f>SUM(B46:AF60)</f>
         <v>15314.390000000003</v>
@@ -37852,7 +37858,7 @@
         <v>58612.759999999995</v>
       </c>
     </row>
-    <row r="63" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B63" s="1">
         <v>45748</v>
       </c>
@@ -37944,7 +37950,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="64" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>5</v>
       </c>
@@ -38007,7 +38013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>0</v>
       </c>
@@ -38037,7 +38043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>16</v>
       </c>
@@ -38082,7 +38088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>34</v>
       </c>
@@ -38100,7 +38106,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>18</v>
       </c>
@@ -38148,7 +38154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>2</v>
       </c>
@@ -38202,7 +38208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>19</v>
       </c>
@@ -38262,7 +38268,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>7</v>
       </c>
@@ -38292,7 +38298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>15</v>
       </c>
@@ -38316,7 +38322,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -38331,7 +38337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>17</v>
       </c>
@@ -38346,7 +38352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>30</v>
       </c>
@@ -38362,7 +38368,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>11</v>
       </c>
@@ -38378,7 +38384,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>1</v>
       </c>
@@ -38394,7 +38400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>20</v>
       </c>
@@ -38409,7 +38415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>8</v>
       </c>
@@ -38448,7 +38454,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>31</v>
       </c>
@@ -38466,7 +38472,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>4</v>
       </c>
@@ -38484,7 +38490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>89</v>
       </c>
@@ -38529,7 +38535,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="84" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q84" s="6">
         <f>SUM(B64:AE82)</f>
         <v>29480.200000000004</v>
@@ -38539,7 +38545,7 @@
         <v>88092.959999999992</v>
       </c>
     </row>
-    <row r="85" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B85" s="1">
         <v>45778</v>
       </c>
@@ -38634,7 +38640,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="86" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>5</v>
       </c>
@@ -38724,7 +38730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>14</v>
       </c>
@@ -38745,7 +38751,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>0</v>
       </c>
@@ -38772,7 +38778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>16</v>
       </c>
@@ -38814,7 +38820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>34</v>
       </c>
@@ -38829,7 +38835,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="91" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>18</v>
       </c>
@@ -38865,7 +38871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>2</v>
       </c>
@@ -38916,7 +38922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>19</v>
       </c>
@@ -38970,7 +38976,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>7</v>
       </c>
@@ -38994,7 +39000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>15</v>
       </c>
@@ -39021,7 +39027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>13</v>
       </c>
@@ -39036,7 +39042,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>17</v>
       </c>
@@ -39056,7 +39062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>30</v>
       </c>
@@ -39074,7 +39080,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>20</v>
       </c>
@@ -39092,7 +39098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>8</v>
       </c>
@@ -39149,7 +39155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>31</v>
       </c>
@@ -39164,7 +39170,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>92</v>
       </c>
@@ -39179,7 +39185,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="104" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>4</v>
       </c>
@@ -39197,7 +39203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>89</v>
       </c>
@@ -39221,7 +39227,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q106" s="6">
         <f>SUM(B86:AF104)</f>
         <v>101069.4</v>
@@ -39237,7 +39243,7 @@
         <v>189162.36</v>
       </c>
     </row>
-    <row r="107" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B107" s="1">
         <v>45809</v>
       </c>
@@ -39329,7 +39335,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="108" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>5</v>
       </c>
@@ -39428,7 +39434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>91</v>
       </c>
@@ -39449,7 +39455,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="110" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>0</v>
       </c>
@@ -39479,7 +39485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>16</v>
       </c>
@@ -39536,7 +39542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>34</v>
       </c>
@@ -39560,7 +39566,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="113" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>18</v>
       </c>
@@ -39593,7 +39599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>2</v>
       </c>
@@ -39635,7 +39641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>19</v>
       </c>
@@ -39683,7 +39689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -39716,7 +39722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>15</v>
       </c>
@@ -39740,7 +39746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>13</v>
       </c>
@@ -39755,7 +39761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>17</v>
       </c>
@@ -39770,7 +39776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>30</v>
       </c>
@@ -39797,7 +39803,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -39830,7 +39836,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>8</v>
       </c>
@@ -39878,7 +39884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>31</v>
       </c>
@@ -39893,7 +39899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>92</v>
       </c>
@@ -39908,7 +39914,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="126" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>4</v>
       </c>
@@ -39929,7 +39935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>89</v>
       </c>
@@ -39974,7 +39980,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="128" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q128" s="6">
         <f>SUM(B108:AE126)</f>
         <v>19562.519999999997</v>
@@ -39984,7 +39990,7 @@
         <v>208724.87999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B129" s="1">
         <v>45839</v>
       </c>
@@ -40079,7 +40085,7 @@
         <v>45869</v>
       </c>
     </row>
-    <row r="130" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -40178,7 +40184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>91</v>
       </c>
@@ -40202,7 +40208,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="132" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>0</v>
       </c>
@@ -40229,7 +40235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>16</v>
       </c>
@@ -40283,7 +40289,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>34</v>
       </c>
@@ -40304,7 +40310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="135" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>18</v>
       </c>
@@ -40343,7 +40349,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>2</v>
       </c>
@@ -40388,7 +40394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>19</v>
       </c>
@@ -40442,7 +40448,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>7</v>
       </c>
@@ -40469,7 +40475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>15</v>
       </c>
@@ -40493,7 +40499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>13</v>
       </c>
@@ -40508,7 +40514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>17</v>
       </c>
@@ -40527,7 +40533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>54</v>
       </c>
@@ -40542,7 +40548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>20</v>
       </c>
@@ -40575,7 +40581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>8</v>
       </c>
@@ -40635,7 +40641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>30</v>
       </c>
@@ -40650,7 +40656,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="147" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>92</v>
       </c>
@@ -40665,7 +40671,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="148" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>4</v>
       </c>
@@ -40686,7 +40692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>89</v>
       </c>
@@ -40722,7 +40728,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q150" s="6">
         <f>SUM(B130:AF148)</f>
         <v>38616.43</v>
@@ -40735,7 +40741,7 @@
         <v>247341.30999999997</v>
       </c>
     </row>
-    <row r="151" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B151" s="1">
         <v>45870</v>
       </c>
@@ -40830,7 +40836,7 @@
         <v>45900</v>
       </c>
     </row>
-    <row r="152" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>5</v>
       </c>
@@ -40929,7 +40935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>91</v>
       </c>
@@ -40950,7 +40956,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="154" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>0</v>
       </c>
@@ -40974,7 +40980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>16</v>
       </c>
@@ -41010,7 +41016,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>34</v>
       </c>
@@ -41028,7 +41034,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="157" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>18</v>
       </c>
@@ -41070,7 +41076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>2</v>
       </c>
@@ -41109,7 +41115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>19</v>
       </c>
@@ -41151,7 +41157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>7</v>
       </c>
@@ -41175,7 +41181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>15</v>
       </c>
@@ -41199,7 +41205,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>13</v>
       </c>
@@ -41214,7 +41220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>17</v>
       </c>
@@ -41232,7 +41238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>53</v>
       </c>
@@ -41253,7 +41259,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="165" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>20</v>
       </c>
@@ -41280,7 +41286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>8</v>
       </c>
@@ -41331,7 +41337,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>94</v>
       </c>
@@ -41349,7 +41355,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="169" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>93</v>
       </c>
@@ -41364,7 +41370,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="170" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>4</v>
       </c>
@@ -41382,7 +41388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>89</v>
       </c>
@@ -41406,7 +41412,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="172" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:43" x14ac:dyDescent="0.3">
       <c r="Q172" s="6">
         <f>SUM(B152:AF170)</f>
         <v>21685.45</v>
@@ -41416,7 +41422,7 @@
         <v>269026.75999999995</v>
       </c>
     </row>
-    <row r="173" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B173" s="1">
         <v>45901</v>
       </c>
@@ -41508,7 +41514,7 @@
         <v>45930</v>
       </c>
     </row>
-    <row r="174" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>5</v>
       </c>
@@ -41601,7 +41607,7 @@
         <v>45922</v>
       </c>
     </row>
-    <row r="175" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>91</v>
       </c>
@@ -41637,7 +41643,7 @@
         <v>25.58</v>
       </c>
     </row>
-    <row r="176" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>0</v>
       </c>
@@ -41676,7 +41682,7 @@
         <v>45.12</v>
       </c>
     </row>
-    <row r="177" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>16</v>
       </c>
@@ -41742,7 +41748,7 @@
         <v>81.27</v>
       </c>
     </row>
-    <row r="178" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>34</v>
       </c>
@@ -41771,7 +41777,7 @@
         <v>151.96999999999997</v>
       </c>
     </row>
-    <row r="179" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>18</v>
       </c>
@@ -41831,7 +41837,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="180" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>2</v>
       </c>
@@ -41873,7 +41879,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="181" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>19</v>
       </c>
@@ -41912,7 +41918,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>7</v>
       </c>
@@ -41939,7 +41945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>15</v>
       </c>
@@ -41970,7 +41976,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="184" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>13</v>
       </c>
@@ -41985,7 +41991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="185" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>17</v>
       </c>
@@ -42000,7 +42006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>53</v>
       </c>
@@ -42018,7 +42024,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="187" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>20</v>
       </c>
@@ -42043,7 +42049,7 @@
         <v>10729</v>
       </c>
     </row>
-    <row r="188" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>31</v>
       </c>
@@ -42098,7 +42104,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>10</v>
       </c>
@@ -42113,7 +42119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>54</v>
       </c>
@@ -42128,7 +42134,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="192" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>94</v>
       </c>
@@ -42146,7 +42152,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="193" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>95</v>
       </c>
@@ -42164,7 +42170,7 @@
         <v>-73</v>
       </c>
     </row>
-    <row r="194" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>4</v>
       </c>
@@ -42194,7 +42200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>89</v>
       </c>
@@ -42236,7 +42242,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="196" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:43" x14ac:dyDescent="0.3">
       <c r="Q196" s="6">
         <f>SUM(B174:AE194)</f>
         <v>55518.2</v>
@@ -42246,7 +42252,7 @@
         <v>324544.95999999996</v>
       </c>
     </row>
-    <row r="197" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B197" s="1">
         <v>45931</v>
       </c>
@@ -42341,7 +42347,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="198" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>5</v>
       </c>
@@ -42425,7 +42431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>91</v>
       </c>
@@ -42443,7 +42449,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="200" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>0</v>
       </c>
@@ -42464,7 +42470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>16</v>
       </c>
@@ -42512,7 +42518,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="202" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>34</v>
       </c>
@@ -42533,7 +42539,7 @@
         <v>88.47</v>
       </c>
     </row>
-    <row r="203" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>18</v>
       </c>
@@ -42584,7 +42590,7 @@
         <v>-46.51</v>
       </c>
     </row>
-    <row r="204" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>2</v>
       </c>
@@ -42627,7 +42633,7 @@
         <v>41.96</v>
       </c>
     </row>
-    <row r="205" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>19</v>
       </c>
@@ -42660,7 +42666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>7</v>
       </c>
@@ -42693,7 +42699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>15</v>
       </c>
@@ -42717,7 +42723,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:43" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>13</v>
       </c>
@@ -42729,7 +42735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>17</v>
       </c>
@@ -42751,7 +42757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>53</v>
       </c>
@@ -42766,7 +42772,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="211" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>20</v>
       </c>
@@ -42796,7 +42802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>31</v>
       </c>
@@ -42832,7 +42838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="214" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>8</v>
       </c>
@@ -42844,7 +42850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>97</v>
       </c>
@@ -42859,7 +42865,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="216" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>4</v>
       </c>
@@ -42880,7 +42886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>89</v>
       </c>
@@ -42925,7 +42931,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="218" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q218" s="6">
         <f>SUM(B198:AF216)</f>
         <v>20311.21</v>
@@ -42935,7 +42941,7 @@
         <v>344856.17</v>
       </c>
     </row>
-    <row r="219" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B219" s="1">
         <v>45962</v>
       </c>
@@ -43027,7 +43033,7 @@
         <v>45991</v>
       </c>
     </row>
-    <row r="220" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>5</v>
       </c>
@@ -43099,7 +43105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>91</v>
       </c>
@@ -43117,7 +43123,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="222" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>0</v>
       </c>
@@ -43138,7 +43144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>16</v>
       </c>
@@ -43177,7 +43183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>33</v>
       </c>
@@ -43192,7 +43198,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="225" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>18</v>
       </c>
@@ -43234,7 +43240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>2</v>
       </c>
@@ -43273,7 +43279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>19</v>
       </c>
@@ -43309,7 +43315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>7</v>
       </c>
@@ -43339,7 +43345,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>15</v>
       </c>
@@ -43363,7 +43369,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>13</v>
       </c>
@@ -43381,7 +43387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>92</v>
       </c>
@@ -43396,7 +43402,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="232" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>53</v>
       </c>
@@ -43411,7 +43417,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="233" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>20</v>
       </c>
@@ -43432,7 +43438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>98</v>
       </c>
@@ -43480,7 +43486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>8</v>
       </c>
@@ -43504,7 +43510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="237" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>10</v>
       </c>
@@ -43522,7 +43528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>4</v>
       </c>
@@ -43546,7 +43552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>89</v>
       </c>
@@ -43588,7 +43594,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="240" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q240" s="6">
         <f>SUM(B220:AE238)</f>
         <v>20025.310000000001</v>
@@ -43598,7 +43604,7 @@
         <v>364881.48</v>
       </c>
     </row>
-    <row r="241" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B241" s="1">
         <v>45992</v>
       </c>
@@ -43693,7 +43699,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="242" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>5</v>
       </c>
@@ -43780,7 +43786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>91</v>
       </c>
@@ -43795,7 +43801,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="244" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>0</v>
       </c>
@@ -43822,7 +43828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>16</v>
       </c>
@@ -43864,7 +43870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="246" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>34</v>
       </c>
@@ -43882,7 +43888,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="247" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>18</v>
       </c>
@@ -43918,7 +43924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>2</v>
       </c>
@@ -43963,7 +43969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>19</v>
       </c>
@@ -44014,7 +44020,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>7</v>
       </c>
@@ -44047,7 +44053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>15</v>
       </c>
@@ -44071,7 +44077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>13</v>
       </c>
@@ -44089,7 +44095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>17</v>
       </c>
@@ -44107,7 +44113,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="254" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>11</v>
       </c>
@@ -44122,7 +44128,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="255" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>20</v>
       </c>
@@ -44155,7 +44161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:35" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>98</v>
       </c>
@@ -44221,7 +44227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="258" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>8</v>
       </c>
@@ -44242,7 +44248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="259" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>10</v>
       </c>
@@ -44260,7 +44266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>4</v>
       </c>
@@ -44284,7 +44290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>89</v>
       </c>
@@ -44320,7 +44326,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="262" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q262" s="6">
         <f>SUM(B242:AF260)</f>
         <v>17088.77</v>
@@ -44342,13 +44348,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF262" xr:uid="{22D8B105-7B1D-4CC9-AC70-0A198640A3CC}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Sahana"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AF262" xr:uid="{22D8B105-7B1D-4CC9-AC70-0A198640A3CC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -44357,7 +44357,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA1C94F-A213-4720-95FA-D2049096F275}">
-  <dimension ref="A1:AK141"/>
+  <dimension ref="A1:AK164"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -48192,9 +48192,51 @@
       <c r="H120">
         <v>54.5</v>
       </c>
+      <c r="J120">
+        <v>28</v>
+      </c>
+      <c r="K120">
+        <v>55</v>
+      </c>
+      <c r="M120">
+        <v>55</v>
+      </c>
+      <c r="N120">
+        <v>28</v>
+      </c>
+      <c r="O120">
+        <v>54.5</v>
+      </c>
+      <c r="P120">
+        <v>55</v>
+      </c>
+      <c r="R120">
+        <v>28</v>
+      </c>
+      <c r="S120">
+        <v>55</v>
+      </c>
+      <c r="U120">
+        <v>55</v>
+      </c>
+      <c r="X120">
+        <v>54.5</v>
+      </c>
+      <c r="Y120">
+        <v>55</v>
+      </c>
+      <c r="AB120">
+        <v>55</v>
+      </c>
+      <c r="AC120">
+        <v>29</v>
+      </c>
+      <c r="AE120">
+        <v>55</v>
+      </c>
       <c r="AH120">
         <f>SUM(B120:AE120)</f>
-        <v>275.5</v>
+        <v>937.5</v>
       </c>
       <c r="AI120" s="2" t="s">
         <v>5</v>
@@ -48204,9 +48246,18 @@
       <c r="A121" t="s">
         <v>91</v>
       </c>
+      <c r="N121">
+        <v>5</v>
+      </c>
+      <c r="U121">
+        <v>5</v>
+      </c>
+      <c r="AB121">
+        <v>5</v>
+      </c>
       <c r="AH121">
         <f>SUM(B121:AE121)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI121" t="s">
         <v>91</v>
@@ -48222,9 +48273,27 @@
       <c r="H122">
         <v>200</v>
       </c>
+      <c r="K122">
+        <v>205</v>
+      </c>
+      <c r="Q122">
+        <v>200</v>
+      </c>
+      <c r="V122">
+        <v>1000</v>
+      </c>
+      <c r="W122">
+        <v>200</v>
+      </c>
+      <c r="Z122">
+        <v>200</v>
+      </c>
+      <c r="AD122">
+        <v>200</v>
+      </c>
       <c r="AH122">
         <f>SUM(B122:AE122)</f>
-        <v>400</v>
+        <v>2405</v>
       </c>
       <c r="AI122" s="2" t="s">
         <v>0</v>
@@ -48243,9 +48312,48 @@
       <c r="H123">
         <v>648</v>
       </c>
+      <c r="J123">
+        <v>60</v>
+      </c>
+      <c r="M123">
+        <v>50</v>
+      </c>
+      <c r="N123">
+        <v>30</v>
+      </c>
+      <c r="P123">
+        <v>64</v>
+      </c>
+      <c r="Q123">
+        <v>70</v>
+      </c>
+      <c r="S123">
+        <v>140</v>
+      </c>
+      <c r="T123">
+        <v>21</v>
+      </c>
+      <c r="V123">
+        <v>670</v>
+      </c>
+      <c r="X123">
+        <v>22</v>
+      </c>
+      <c r="Z123">
+        <v>30</v>
+      </c>
+      <c r="AA123">
+        <v>10</v>
+      </c>
+      <c r="AC123">
+        <v>60</v>
+      </c>
+      <c r="AE123">
+        <v>50</v>
+      </c>
       <c r="AH123">
         <f t="shared" ref="AH123:AH140" si="5">SUM(B123:AE123)</f>
-        <v>734</v>
+        <v>2011</v>
       </c>
       <c r="AI123" s="2" t="s">
         <v>16</v>
@@ -48258,9 +48366,18 @@
       <c r="H124">
         <v>69.05</v>
       </c>
+      <c r="Q124">
+        <v>490</v>
+      </c>
+      <c r="Z124">
+        <v>449</v>
+      </c>
+      <c r="AA124">
+        <v>90</v>
+      </c>
       <c r="AH124">
         <f t="shared" si="5"/>
-        <v>69.05</v>
+        <v>1098.05</v>
       </c>
       <c r="AI124" s="2" t="s">
         <v>34</v>
@@ -48279,9 +48396,27 @@
       <c r="J125">
         <v>177</v>
       </c>
+      <c r="L125">
+        <v>511.61</v>
+      </c>
+      <c r="M125">
+        <v>412</v>
+      </c>
+      <c r="O125">
+        <v>160</v>
+      </c>
+      <c r="R125">
+        <v>60</v>
+      </c>
+      <c r="X125">
+        <v>622</v>
+      </c>
+      <c r="AA125">
+        <v>300</v>
+      </c>
       <c r="AH125">
         <f t="shared" si="5"/>
-        <v>1691.72</v>
+        <v>3757.33</v>
       </c>
       <c r="AI125" s="2" t="s">
         <v>18</v>
@@ -48306,9 +48441,36 @@
       <c r="H126">
         <v>250</v>
       </c>
+      <c r="K126">
+        <v>27</v>
+      </c>
+      <c r="N126">
+        <v>48</v>
+      </c>
+      <c r="Q126">
+        <v>70</v>
+      </c>
+      <c r="S126">
+        <v>180</v>
+      </c>
+      <c r="V126">
+        <v>180</v>
+      </c>
+      <c r="X126">
+        <v>50</v>
+      </c>
+      <c r="Y126">
+        <v>50</v>
+      </c>
+      <c r="AA126">
+        <v>47</v>
+      </c>
+      <c r="AC126">
+        <v>50</v>
+      </c>
       <c r="AH126">
         <f t="shared" si="5"/>
-        <v>375</v>
+        <v>1077</v>
       </c>
       <c r="AI126" s="2" t="s">
         <v>2</v>
@@ -48324,9 +48486,21 @@
       <c r="G127">
         <v>80</v>
       </c>
+      <c r="L127">
+        <v>30</v>
+      </c>
+      <c r="O127">
+        <v>97</v>
+      </c>
+      <c r="U127">
+        <v>40</v>
+      </c>
+      <c r="X127">
+        <v>26</v>
+      </c>
       <c r="AH127">
         <f t="shared" si="5"/>
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="AI127" s="2" t="s">
         <v>19</v>
@@ -48345,9 +48519,21 @@
       <c r="H128">
         <v>50</v>
       </c>
+      <c r="T128">
+        <v>50</v>
+      </c>
+      <c r="U128">
+        <v>50</v>
+      </c>
+      <c r="V128">
+        <v>100</v>
+      </c>
+      <c r="AC128">
+        <v>50</v>
+      </c>
       <c r="AH128">
         <f t="shared" si="5"/>
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="AI128" s="2" t="s">
         <v>7</v>
@@ -48357,9 +48543,21 @@
       <c r="A129" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="K129">
+        <v>396</v>
+      </c>
+      <c r="L129">
+        <v>169</v>
+      </c>
+      <c r="M129">
+        <v>129</v>
+      </c>
+      <c r="N129">
+        <v>468</v>
+      </c>
       <c r="AH129">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1162</v>
       </c>
       <c r="AI129" s="2" t="s">
         <v>15</v>
@@ -48369,9 +48567,12 @@
       <c r="A130" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="N130">
+        <v>270</v>
+      </c>
       <c r="AH130">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI130" s="2" t="s">
         <v>13</v>
@@ -48396,9 +48597,12 @@
       <c r="A132" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="V132">
+        <v>80</v>
+      </c>
       <c r="AH132">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AI132" s="2" t="s">
         <v>99</v>
@@ -48417,9 +48621,18 @@
       <c r="H133">
         <v>40</v>
       </c>
+      <c r="K133">
+        <v>10</v>
+      </c>
+      <c r="L133">
+        <v>500</v>
+      </c>
+      <c r="W133">
+        <v>239</v>
+      </c>
       <c r="AH133">
         <f t="shared" si="5"/>
-        <v>837.82</v>
+        <v>1586.8200000000002</v>
       </c>
       <c r="AI133" s="2" t="s">
         <v>20</v>
@@ -48427,14 +48640,17 @@
     </row>
     <row r="134" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
+      </c>
+      <c r="Y134">
+        <v>119</v>
       </c>
       <c r="AH134">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AI134" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="135" spans="1:36" x14ac:dyDescent="0.3">
@@ -48453,9 +48669,18 @@
       <c r="A136" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="Z136">
+        <v>35</v>
+      </c>
+      <c r="AB136">
+        <v>200</v>
+      </c>
+      <c r="AD136">
+        <v>8</v>
+      </c>
       <c r="AH136">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="AI136" s="2" t="s">
         <v>12</v>
@@ -48471,9 +48696,27 @@
       <c r="C137">
         <v>40</v>
       </c>
+      <c r="L137">
+        <v>20</v>
+      </c>
+      <c r="N137">
+        <v>10</v>
+      </c>
+      <c r="Q137">
+        <v>100</v>
+      </c>
+      <c r="S137">
+        <v>90</v>
+      </c>
+      <c r="U137">
+        <v>10</v>
+      </c>
+      <c r="AA137">
+        <v>20</v>
+      </c>
       <c r="AH137">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="AI137" s="2" t="s">
         <v>30</v>
@@ -48483,9 +48726,18 @@
       <c r="A138" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="X138">
+        <v>98</v>
+      </c>
+      <c r="AD138">
+        <v>40</v>
+      </c>
+      <c r="AE138">
+        <v>25</v>
+      </c>
       <c r="AH138">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="AI138" s="2" t="s">
         <v>8</v>
@@ -48495,9 +48747,21 @@
       <c r="A139" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="V139">
+        <v>30</v>
+      </c>
+      <c r="X139">
+        <v>10</v>
+      </c>
+      <c r="AC139">
+        <v>5</v>
+      </c>
+      <c r="AD139">
+        <v>12</v>
+      </c>
       <c r="AH139">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AI139" s="2" t="s">
         <v>4</v>
@@ -48519,9 +48783,39 @@
       <c r="J140" s="13">
         <v>26</v>
       </c>
+      <c r="K140" s="13">
+        <v>198</v>
+      </c>
+      <c r="L140" s="13">
+        <v>357</v>
+      </c>
+      <c r="M140" s="13">
+        <v>28</v>
+      </c>
+      <c r="P140" s="13">
+        <v>340</v>
+      </c>
+      <c r="R140" s="13">
+        <v>26</v>
+      </c>
+      <c r="S140" s="13">
+        <v>50</v>
+      </c>
+      <c r="U140" s="13">
+        <v>26</v>
+      </c>
+      <c r="X140" s="13">
+        <v>461.62</v>
+      </c>
+      <c r="Y140" s="13">
+        <v>54</v>
+      </c>
+      <c r="AB140" s="13">
+        <v>26</v>
+      </c>
       <c r="AH140">
         <f t="shared" si="5"/>
-        <v>142</v>
+        <v>1708.62</v>
       </c>
       <c r="AI140" s="2" t="s">
         <v>89</v>
@@ -48530,11 +48824,479 @@
     <row r="141" spans="1:36" x14ac:dyDescent="0.3">
       <c r="Q141" s="6">
         <f>SUM(B120:AE139)</f>
-        <v>5339.91</v>
+        <v>16631.52</v>
       </c>
       <c r="AJ141">
         <f>SUM(AJ118,Q141)</f>
-        <v>323666.46999999997</v>
+        <v>334958.08000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="B142" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C142" s="1">
+        <v>46205</v>
+      </c>
+      <c r="D142" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E142" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F142" s="1">
+        <v>46208</v>
+      </c>
+      <c r="G142" s="1">
+        <v>46209</v>
+      </c>
+      <c r="H142" s="1">
+        <v>46210</v>
+      </c>
+      <c r="I142" s="1">
+        <v>46211</v>
+      </c>
+      <c r="J142" s="1">
+        <v>46212</v>
+      </c>
+      <c r="K142" s="1">
+        <v>46213</v>
+      </c>
+      <c r="L142" s="1">
+        <v>46214</v>
+      </c>
+      <c r="M142" s="1">
+        <v>46215</v>
+      </c>
+      <c r="N142" s="1">
+        <v>46216</v>
+      </c>
+      <c r="O142" s="1">
+        <v>46217</v>
+      </c>
+      <c r="P142" s="1">
+        <v>46218</v>
+      </c>
+      <c r="Q142" s="1">
+        <v>46219</v>
+      </c>
+      <c r="R142" s="1">
+        <v>46220</v>
+      </c>
+      <c r="S142" s="1">
+        <v>46221</v>
+      </c>
+      <c r="T142" s="1">
+        <v>46222</v>
+      </c>
+      <c r="U142" s="1">
+        <v>46223</v>
+      </c>
+      <c r="V142" s="1">
+        <v>46224</v>
+      </c>
+      <c r="W142" s="1">
+        <v>46225</v>
+      </c>
+      <c r="X142" s="1">
+        <v>46226</v>
+      </c>
+      <c r="Y142" s="1">
+        <v>46227</v>
+      </c>
+      <c r="Z142" s="1">
+        <v>46228</v>
+      </c>
+      <c r="AA142" s="1">
+        <v>46229</v>
+      </c>
+      <c r="AB142" s="1">
+        <v>46230</v>
+      </c>
+      <c r="AC142" s="1">
+        <v>46231</v>
+      </c>
+      <c r="AD142" s="1">
+        <v>46232</v>
+      </c>
+      <c r="AE142" s="1">
+        <v>46233</v>
+      </c>
+      <c r="AF142" s="1">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="143" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143">
+        <v>28</v>
+      </c>
+      <c r="C143">
+        <v>28</v>
+      </c>
+      <c r="D143">
+        <v>55</v>
+      </c>
+      <c r="E143">
+        <v>26.25</v>
+      </c>
+      <c r="F143">
+        <v>27</v>
+      </c>
+      <c r="H143">
+        <v>55</v>
+      </c>
+      <c r="J143">
+        <v>55</v>
+      </c>
+      <c r="AH143">
+        <f>SUM(B143:AF143)</f>
+        <v>274.25</v>
+      </c>
+      <c r="AI143" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH144">
+        <f>SUM(B144:AF144)</f>
+        <v>0</v>
+      </c>
+      <c r="AI144" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>200</v>
+      </c>
+      <c r="AH145">
+        <f t="shared" ref="AH145:AH163" si="6">SUM(B145:AF145)</f>
+        <v>200</v>
+      </c>
+      <c r="AI145" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146">
+        <v>11</v>
+      </c>
+      <c r="E146">
+        <v>69.64</v>
+      </c>
+      <c r="F146">
+        <v>768</v>
+      </c>
+      <c r="G146">
+        <v>16</v>
+      </c>
+      <c r="J146">
+        <v>30</v>
+      </c>
+      <c r="AH146">
+        <f t="shared" si="6"/>
+        <v>894.64</v>
+      </c>
+      <c r="AI146" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H147">
+        <v>224</v>
+      </c>
+      <c r="AH147">
+        <f t="shared" si="6"/>
+        <v>224</v>
+      </c>
+      <c r="AI147" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J148">
+        <v>1200</v>
+      </c>
+      <c r="AH148">
+        <f t="shared" si="6"/>
+        <v>1200</v>
+      </c>
+      <c r="AI148" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B149">
+        <v>90</v>
+      </c>
+      <c r="E149">
+        <v>1831.52</v>
+      </c>
+      <c r="F149">
+        <v>449.35</v>
+      </c>
+      <c r="AH149">
+        <f t="shared" si="6"/>
+        <v>2370.87</v>
+      </c>
+      <c r="AI149" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150">
+        <v>30</v>
+      </c>
+      <c r="D150">
+        <v>33</v>
+      </c>
+      <c r="F150">
+        <v>120</v>
+      </c>
+      <c r="I150">
+        <v>91.81</v>
+      </c>
+      <c r="AH150">
+        <f t="shared" si="6"/>
+        <v>274.81</v>
+      </c>
+      <c r="AI150" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151">
+        <v>104</v>
+      </c>
+      <c r="F151">
+        <v>30</v>
+      </c>
+      <c r="I151">
+        <v>60</v>
+      </c>
+      <c r="AH151">
+        <f t="shared" si="6"/>
+        <v>194</v>
+      </c>
+      <c r="AI151" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152">
+        <v>50</v>
+      </c>
+      <c r="F152">
+        <v>70</v>
+      </c>
+      <c r="AH152">
+        <f t="shared" si="6"/>
+        <v>120</v>
+      </c>
+      <c r="AI152" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH153">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI153" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH154">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI154" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155">
+        <v>556.82000000000005</v>
+      </c>
+      <c r="AH155">
+        <f t="shared" si="6"/>
+        <v>556.82000000000005</v>
+      </c>
+      <c r="AI155" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F156">
+        <v>80</v>
+      </c>
+      <c r="AH156">
+        <f t="shared" si="6"/>
+        <v>80</v>
+      </c>
+      <c r="AI156" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="157" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K157">
+        <v>32050</v>
+      </c>
+      <c r="AH157">
+        <f t="shared" si="6"/>
+        <v>32050</v>
+      </c>
+      <c r="AI157" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH158">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI158" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E159">
+        <v>500</v>
+      </c>
+      <c r="AH159">
+        <f t="shared" si="6"/>
+        <v>500</v>
+      </c>
+      <c r="AI159" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH160">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI160" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161">
+        <v>50</v>
+      </c>
+      <c r="AH161">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="AI161" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G162">
+        <v>140</v>
+      </c>
+      <c r="J162">
+        <v>30</v>
+      </c>
+      <c r="AH162">
+        <f t="shared" si="6"/>
+        <v>170</v>
+      </c>
+      <c r="AI162" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F163" s="13">
+        <v>30</v>
+      </c>
+      <c r="G163" s="13">
+        <v>151</v>
+      </c>
+      <c r="J163" s="13">
+        <v>386</v>
+      </c>
+      <c r="AH163">
+        <f t="shared" si="6"/>
+        <v>567</v>
+      </c>
+      <c r="AI163" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="164" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="Q164" s="6">
+        <f>SUM(B143:AF162)</f>
+        <v>39159.39</v>
+      </c>
+      <c r="AJ164">
+        <f>SUM(AJ141,Q164)</f>
+        <v>374117.47000000003</v>
       </c>
     </row>
   </sheetData>
